--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R3" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,28 +872,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B4" t="n">
-        <v>91662</v>
+        <v>91641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,44 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R4" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,74 +970,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130236402</v>
+        <v>130228760</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>97704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576421</v>
+        <v>576180</v>
       </c>
       <c r="R5" t="n">
-        <v>6342895</v>
+        <v>6343221</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,67 +1067,73 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130228760</v>
+        <v>130236402</v>
       </c>
       <c r="B6" t="n">
-        <v>97704</v>
+        <v>91641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576180</v>
+        <v>576421</v>
       </c>
       <c r="R6" t="n">
-        <v>6343221</v>
+        <v>6342895</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,18 +1171,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130226133</v>
+        <v>130227038</v>
       </c>
       <c r="B8" t="n">
         <v>57738</v>
@@ -1322,7 +1322,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576166</v>
+        <v>576189</v>
       </c>
       <c r="R8" t="n">
-        <v>6343217</v>
+        <v>6343133</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130227038</v>
+        <v>130226133</v>
       </c>
       <c r="B9" t="n">
         <v>57738</v>
@@ -1424,7 +1424,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576189</v>
+        <v>576166</v>
       </c>
       <c r="R9" t="n">
-        <v>6343133</v>
+        <v>6343217</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,45 +1495,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130226469</v>
+        <v>130227799</v>
       </c>
       <c r="B10" t="n">
-        <v>92094</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576198</v>
+        <v>576368</v>
       </c>
       <c r="R10" t="n">
-        <v>6343287</v>
+        <v>6343022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,57 +1590,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Emelie Westerberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Emelie Westerberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130227799</v>
+        <v>130226469</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>92094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576368</v>
+        <v>576198</v>
       </c>
       <c r="R11" t="n">
-        <v>6343022</v>
+        <v>6343287</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,19 +1697,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emelie Westerberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emelie Westerberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130227745</v>
+        <v>130228644</v>
       </c>
       <c r="B12" t="n">
         <v>79714</v>
@@ -1740,17 +1740,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576451</v>
+        <v>576518</v>
       </c>
       <c r="R12" t="n">
-        <v>6343018</v>
+        <v>6342991</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228206</v>
+        <v>130227745</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,42 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576360</v>
+        <v>576451</v>
       </c>
       <c r="R13" t="n">
-        <v>6342961</v>
+        <v>6343018</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,19 +1874,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,22 +1891,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228644</v>
+        <v>130228206</v>
       </c>
       <c r="B14" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,37 +1914,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576518</v>
+        <v>576360</v>
       </c>
       <c r="R14" t="n">
-        <v>6342991</v>
+        <v>6342961</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,9 +1976,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,12 +2003,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130226405</v>
+        <v>130235360</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>91641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,37 +2439,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576198</v>
+        <v>576131</v>
       </c>
       <c r="R19" t="n">
-        <v>6343287</v>
+        <v>6343160</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2496,49 +2503,40 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130235360</v>
+        <v>130226405</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>79714</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,44 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576131</v>
+        <v>576198</v>
       </c>
       <c r="R20" t="n">
-        <v>6343160</v>
+        <v>6343287</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2610,40 +2601,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B21" t="n">
-        <v>91662</v>
+        <v>57738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,37 +2651,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R21" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2708,19 +2713,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,22 +2730,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B22" t="n">
-        <v>57738</v>
+        <v>91662</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,42 +2753,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R22" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,9 +2810,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,19 +2837,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130226031</v>
+        <v>130228309</v>
       </c>
       <c r="B23" t="n">
         <v>57738</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576189</v>
+        <v>576518</v>
       </c>
       <c r="R23" t="n">
-        <v>6343254</v>
+        <v>6342991</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2951,7 +2951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130227753</v>
+        <v>130226031</v>
       </c>
       <c r="B24" t="n">
         <v>57738</v>
@@ -2980,16 +2980,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576198</v>
+        <v>576189</v>
       </c>
       <c r="R24" t="n">
-        <v>6343287</v>
+        <v>6343254</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3019,19 +3024,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,19 +3041,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130228309</v>
+        <v>130227753</v>
       </c>
       <c r="B25" t="n">
         <v>57738</v>
@@ -3087,21 +3082,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576518</v>
+        <v>576198</v>
       </c>
       <c r="R25" t="n">
-        <v>6342991</v>
+        <v>6343287</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3131,9 +3121,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,19 +3148,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B26" t="n">
         <v>57738</v>
@@ -3188,10 +3188,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3200,13 +3209,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R26" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3244,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3245,7 +3254,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3272,7 +3281,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B27" t="n">
         <v>57738</v>
@@ -3300,19 +3309,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R27" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3393,52 +3393,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130225961</v>
+        <v>130236453</v>
       </c>
       <c r="B28" t="n">
-        <v>92291</v>
+        <v>57738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576198</v>
+        <v>576441</v>
       </c>
       <c r="R28" t="n">
-        <v>6343287</v>
+        <v>6342906</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,19 +3473,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3492,72 +3490,64 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130236453</v>
+        <v>130225961</v>
       </c>
       <c r="B29" t="n">
-        <v>57738</v>
+        <v>92291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576441</v>
+        <v>576198</v>
       </c>
       <c r="R29" t="n">
-        <v>6342906</v>
+        <v>6343287</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,9 +3574,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>130235558</v>
       </c>
       <c r="B3" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130227842</v>
       </c>
       <c r="B4" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>130228760</v>
       </c>
       <c r="B5" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>130236402</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,37 +1190,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130225954</v>
+        <v>130226133</v>
       </c>
       <c r="B7" t="n">
-        <v>92291</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576207</v>
+        <v>576166</v>
       </c>
       <c r="R7" t="n">
-        <v>6343282</v>
+        <v>6343217</v>
       </c>
       <c r="S7" t="n">
         <v>30</v>
@@ -1294,7 +1295,7 @@
         <v>130227038</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,38 +1394,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130226133</v>
+        <v>130225954</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>92378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576166</v>
+        <v>576207</v>
       </c>
       <c r="R9" t="n">
-        <v>6343217</v>
+        <v>6343282</v>
       </c>
       <c r="S9" t="n">
         <v>30</v>
@@ -1498,7 +1498,7 @@
         <v>130227799</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>130226469</v>
       </c>
       <c r="B11" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228644</v>
+        <v>130228206</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,37 +1720,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576518</v>
+        <v>576360</v>
       </c>
       <c r="R12" t="n">
-        <v>6342991</v>
+        <v>6342961</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,9 +1782,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,22 +1809,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130227745</v>
+        <v>130228644</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,17 +1852,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576451</v>
+        <v>576518</v>
       </c>
       <c r="R13" t="n">
-        <v>6343018</v>
+        <v>6342991</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1903,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228206</v>
+        <v>130227745</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,42 +1929,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576360</v>
+        <v>576451</v>
       </c>
       <c r="R14" t="n">
-        <v>6342961</v>
+        <v>6343018</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1976,19 +1986,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,12 +2003,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2018,7 +2018,7 @@
         <v>130227694</v>
       </c>
       <c r="B15" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>130226464</v>
       </c>
       <c r="B16" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130227384</v>
       </c>
       <c r="B17" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130226314</v>
+        <v>130226405</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2337,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576147</v>
+        <v>576198</v>
       </c>
       <c r="R18" t="n">
-        <v>6343161</v>
+        <v>6343287</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,9 +2394,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,22 +2421,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130235360</v>
+        <v>130226314</v>
       </c>
       <c r="B19" t="n">
-        <v>91641</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,44 +2444,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576131</v>
+        <v>576147</v>
       </c>
       <c r="R19" t="n">
-        <v>6343160</v>
+        <v>6343161</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2514,29 +2517,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226405</v>
+        <v>130235360</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2546,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576198</v>
+        <v>576131</v>
       </c>
       <c r="R20" t="n">
-        <v>6343287</v>
+        <v>6343160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,49 +2610,40 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>91749</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,42 +2651,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R21" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2713,9 +2708,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,22 +2735,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B22" t="n">
-        <v>91662</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,37 +2758,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R22" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,19 +2820,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,22 +2837,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228309</v>
+        <v>130227753</v>
       </c>
       <c r="B23" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2878,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576518</v>
+        <v>576198</v>
       </c>
       <c r="R23" t="n">
-        <v>6342991</v>
+        <v>6343287</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2922,9 +2917,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2939,12 +2944,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2954,7 +2959,7 @@
         <v>130226031</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227753</v>
+        <v>130228309</v>
       </c>
       <c r="B25" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,16 +3087,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576198</v>
+        <v>576518</v>
       </c>
       <c r="R25" t="n">
-        <v>6343287</v>
+        <v>6342991</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,22 +3148,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,19 +3188,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3209,13 +3200,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R26" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3244,7 +3235,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3254,7 +3245,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B27" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,10 +3300,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R27" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3393,60 +3393,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236453</v>
+        <v>130225961</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>92378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576441</v>
+        <v>576198</v>
       </c>
       <c r="R28" t="n">
-        <v>6342906</v>
+        <v>6343287</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,9 +3465,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3490,64 +3492,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130225961</v>
+        <v>130236453</v>
       </c>
       <c r="B29" t="n">
-        <v>92291</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576198</v>
+        <v>576441</v>
       </c>
       <c r="R29" t="n">
-        <v>6343287</v>
+        <v>6342906</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,19 +3584,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
         <v>130236380</v>
       </c>
       <c r="B30" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91749</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R3" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,28 +872,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B4" t="n">
-        <v>91749</v>
+        <v>91728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,44 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R4" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +970,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228644</v>
+        <v>130228206</v>
       </c>
       <c r="B12" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,37 +1720,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576518</v>
+        <v>576360</v>
       </c>
       <c r="R12" t="n">
-        <v>6342991</v>
+        <v>6342961</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,9 +1782,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,19 +1809,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130227745</v>
+        <v>130228644</v>
       </c>
       <c r="B13" t="n">
         <v>79799</v>
@@ -1837,17 +1852,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576451</v>
+        <v>576518</v>
       </c>
       <c r="R13" t="n">
-        <v>6343018</v>
+        <v>6342991</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1903,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228206</v>
+        <v>130227745</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,42 +1929,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576360</v>
+        <v>576451</v>
       </c>
       <c r="R14" t="n">
-        <v>6342961</v>
+        <v>6343018</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1976,19 +1986,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,12 +2003,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B3" t="n">
-        <v>91749</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,44 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R3" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,29 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B4" t="n">
-        <v>91728</v>
+        <v>91749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,37 +894,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R4" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,18 +969,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228206</v>
+        <v>130228644</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,42 +1720,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576360</v>
+        <v>576518</v>
       </c>
       <c r="R12" t="n">
-        <v>6342961</v>
+        <v>6342991</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,19 +1777,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,19 +1794,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228644</v>
+        <v>130227745</v>
       </c>
       <c r="B13" t="n">
         <v>79799</v>
@@ -1852,17 +1837,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576518</v>
+        <v>576451</v>
       </c>
       <c r="R13" t="n">
-        <v>6342991</v>
+        <v>6343018</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1918,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130227745</v>
+        <v>130228206</v>
       </c>
       <c r="B14" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,37 +1914,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576451</v>
+        <v>576360</v>
       </c>
       <c r="R14" t="n">
-        <v>6343018</v>
+        <v>6342961</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,9 +1976,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,12 +2003,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3393,60 +3393,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236453</v>
+        <v>130225961</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>92378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576441</v>
+        <v>576198</v>
       </c>
       <c r="R28" t="n">
-        <v>6342906</v>
+        <v>6343287</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,9 +3465,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3490,64 +3492,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130225961</v>
+        <v>130236453</v>
       </c>
       <c r="B29" t="n">
-        <v>92378</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576198</v>
+        <v>576441</v>
       </c>
       <c r="R29" t="n">
-        <v>6343287</v>
+        <v>6342906</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,19 +3584,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>130227842</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>130235558</v>
       </c>
       <c r="B4" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>130236402</v>
       </c>
       <c r="B5" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>130228760</v>
       </c>
       <c r="B6" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130225954</v>
       </c>
       <c r="B7" t="n">
-        <v>92378</v>
+        <v>92381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130227038</v>
+        <v>130226133</v>
       </c>
       <c r="B8" t="n">
         <v>57823</v>
@@ -1322,7 +1322,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576189</v>
+        <v>576166</v>
       </c>
       <c r="R8" t="n">
-        <v>6343133</v>
+        <v>6343217</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130226133</v>
+        <v>130227038</v>
       </c>
       <c r="B9" t="n">
         <v>57823</v>
@@ -1424,7 +1424,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576166</v>
+        <v>576189</v>
       </c>
       <c r="R9" t="n">
-        <v>6343217</v>
+        <v>6343133</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130226469</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>130228644</v>
       </c>
       <c r="B12" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>130227745</v>
       </c>
       <c r="B13" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130227694</v>
       </c>
       <c r="B15" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>130226464</v>
       </c>
       <c r="B16" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130227384</v>
       </c>
       <c r="B17" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>130235360</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130226405</v>
+        <v>130226314</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,37 +2442,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576198</v>
+        <v>576147</v>
       </c>
       <c r="R19" t="n">
-        <v>6343287</v>
+        <v>6343161</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,19 +2504,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,22 +2521,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226314</v>
+        <v>130226405</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>79802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576147</v>
+        <v>576198</v>
       </c>
       <c r="R20" t="n">
-        <v>6343161</v>
+        <v>6343287</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2611,9 +2601,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,22 +2628,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>91752</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,42 +2651,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R21" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2713,9 +2708,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,22 +2735,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B22" t="n">
-        <v>91749</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,37 +2758,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R22" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,19 +2820,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,12 +2837,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130226031</v>
+        <v>130227753</v>
       </c>
       <c r="B24" t="n">
         <v>57823</v>
@@ -2980,21 +2980,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576189</v>
+        <v>576198</v>
       </c>
       <c r="R24" t="n">
-        <v>6343254</v>
+        <v>6343287</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3024,9 +3019,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,19 +3046,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227753</v>
+        <v>130226031</v>
       </c>
       <c r="B25" t="n">
         <v>57823</v>
@@ -3082,16 +3087,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576198</v>
+        <v>576189</v>
       </c>
       <c r="R25" t="n">
-        <v>6343287</v>
+        <v>6343254</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,12 +3148,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3393,52 +3393,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130225961</v>
+        <v>130236453</v>
       </c>
       <c r="B28" t="n">
-        <v>92378</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576198</v>
+        <v>576441</v>
       </c>
       <c r="R28" t="n">
-        <v>6343287</v>
+        <v>6342906</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,19 +3473,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3492,72 +3490,64 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130236453</v>
+        <v>130225961</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>92381</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576441</v>
+        <v>576198</v>
       </c>
       <c r="R29" t="n">
-        <v>6342906</v>
+        <v>6343287</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,9 +3574,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
         <v>130236380</v>
       </c>
       <c r="B30" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B3" t="n">
-        <v>91731</v>
+        <v>91778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R3" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,28 +872,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B4" t="n">
-        <v>91752</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,44 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R4" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,74 +970,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130236402</v>
+        <v>130228760</v>
       </c>
       <c r="B5" t="n">
-        <v>91731</v>
+        <v>97820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576421</v>
+        <v>576180</v>
       </c>
       <c r="R5" t="n">
-        <v>6342895</v>
+        <v>6343221</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,67 +1067,73 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130228760</v>
+        <v>130236402</v>
       </c>
       <c r="B6" t="n">
-        <v>97794</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576180</v>
+        <v>576421</v>
       </c>
       <c r="R6" t="n">
-        <v>6343221</v>
+        <v>6342895</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,55 +1171,57 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130225954</v>
+        <v>130226133</v>
       </c>
       <c r="B7" t="n">
-        <v>92381</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576207</v>
+        <v>576166</v>
       </c>
       <c r="R7" t="n">
-        <v>6343282</v>
+        <v>6343217</v>
       </c>
       <c r="S7" t="n">
         <v>30</v>
@@ -1291,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130226133</v>
+        <v>130227038</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,7 +1323,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1331,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576166</v>
+        <v>576189</v>
       </c>
       <c r="R8" t="n">
-        <v>6343217</v>
+        <v>6343133</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,38 +1394,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130227038</v>
+        <v>130225954</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>92407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576189</v>
+        <v>576207</v>
       </c>
       <c r="R9" t="n">
-        <v>6343133</v>
+        <v>6343282</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130226469</v>
       </c>
       <c r="B10" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>130227799</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>130228644</v>
       </c>
       <c r="B12" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>130227745</v>
       </c>
       <c r="B13" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>130228206</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130227694</v>
       </c>
       <c r="B15" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>130226464</v>
       </c>
       <c r="B16" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130227384</v>
       </c>
       <c r="B17" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>130235360</v>
       </c>
       <c r="B18" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130226314</v>
+        <v>130226405</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>79828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,42 +2442,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576147</v>
+        <v>576198</v>
       </c>
       <c r="R19" t="n">
-        <v>6343161</v>
+        <v>6343287</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2504,9 +2499,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,22 +2526,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226405</v>
+        <v>130226314</v>
       </c>
       <c r="B20" t="n">
-        <v>79802</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2549,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576198</v>
+        <v>576147</v>
       </c>
       <c r="R20" t="n">
-        <v>6343287</v>
+        <v>6343161</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,19 +2611,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         <v>130226508</v>
       </c>
       <c r="B21" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130227640</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>130228309</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130227753</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130226031</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>130226739</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>130226330</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>130236453</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>130225961</v>
       </c>
       <c r="B29" t="n">
-        <v>92381</v>
+        <v>92407</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>130236380</v>
       </c>
       <c r="B30" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -1190,38 +1190,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130226133</v>
+        <v>130225954</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>92407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576166</v>
+        <v>576207</v>
       </c>
       <c r="R7" t="n">
-        <v>6343217</v>
+        <v>6343282</v>
       </c>
       <c r="S7" t="n">
         <v>30</v>
@@ -1292,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130227038</v>
+        <v>130226133</v>
       </c>
       <c r="B8" t="n">
         <v>57849</v>
@@ -1323,7 +1322,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1332,13 +1331,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576189</v>
+        <v>576166</v>
       </c>
       <c r="R8" t="n">
-        <v>6343133</v>
+        <v>6343217</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,37 +1393,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130225954</v>
+        <v>130227038</v>
       </c>
       <c r="B9" t="n">
-        <v>92407</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576207</v>
+        <v>576189</v>
       </c>
       <c r="R9" t="n">
-        <v>6343282</v>
+        <v>6343133</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228644</v>
+        <v>130228206</v>
       </c>
       <c r="B12" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,37 +1720,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576518</v>
+        <v>576360</v>
       </c>
       <c r="R12" t="n">
-        <v>6342991</v>
+        <v>6342961</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,9 +1782,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,19 +1809,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130227745</v>
+        <v>130228644</v>
       </c>
       <c r="B13" t="n">
         <v>79828</v>
@@ -1837,17 +1852,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576451</v>
+        <v>576518</v>
       </c>
       <c r="R13" t="n">
-        <v>6343018</v>
+        <v>6342991</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1903,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130228206</v>
+        <v>130227745</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,42 +1929,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576360</v>
+        <v>576451</v>
       </c>
       <c r="R14" t="n">
-        <v>6342961</v>
+        <v>6343018</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1976,19 +1986,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,12 +2003,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B3" t="n">
-        <v>91778</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,44 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R3" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,29 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>91779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,37 +894,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R4" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,66 +969,74 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130228760</v>
+        <v>130236402</v>
       </c>
       <c r="B5" t="n">
-        <v>97820</v>
+        <v>91758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576180</v>
+        <v>576421</v>
       </c>
       <c r="R5" t="n">
-        <v>6343221</v>
+        <v>6342895</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,73 +1074,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130236402</v>
+        <v>130228760</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>97821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576421</v>
+        <v>576180</v>
       </c>
       <c r="R6" t="n">
-        <v>6342895</v>
+        <v>6343221</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,19 +1172,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
         <v>130225954</v>
       </c>
       <c r="B7" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130226469</v>
       </c>
       <c r="B10" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130227694</v>
       </c>
       <c r="B15" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130227384</v>
       </c>
       <c r="B17" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130235360</v>
+        <v>130226405</v>
       </c>
       <c r="B18" t="n">
-        <v>91757</v>
+        <v>79828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,44 +2337,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576131</v>
+        <v>576198</v>
       </c>
       <c r="R18" t="n">
-        <v>6343160</v>
+        <v>6343287</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,40 +2394,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130226405</v>
+        <v>130226314</v>
       </c>
       <c r="B19" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,37 +2444,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576198</v>
+        <v>576147</v>
       </c>
       <c r="R19" t="n">
-        <v>6343287</v>
+        <v>6343161</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,19 +2506,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,22 +2523,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226314</v>
+        <v>130235360</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>91758</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,42 +2546,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576147</v>
+        <v>576131</v>
       </c>
       <c r="R20" t="n">
-        <v>6343161</v>
+        <v>6343160</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,18 +2621,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         <v>130226508</v>
       </c>
       <c r="B21" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130227753</v>
+        <v>130226031</v>
       </c>
       <c r="B24" t="n">
         <v>57849</v>
@@ -2980,16 +2980,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576198</v>
+        <v>576189</v>
       </c>
       <c r="R24" t="n">
-        <v>6343287</v>
+        <v>6343254</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3019,19 +3024,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,19 +3041,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130226031</v>
+        <v>130227753</v>
       </c>
       <c r="B25" t="n">
         <v>57849</v>
@@ -3087,21 +3082,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576189</v>
+        <v>576198</v>
       </c>
       <c r="R25" t="n">
-        <v>6343254</v>
+        <v>6343287</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3131,9 +3121,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,12 +3148,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3393,60 +3393,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130236453</v>
+        <v>130225961</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>92408</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576441</v>
+        <v>576198</v>
       </c>
       <c r="R28" t="n">
-        <v>6342906</v>
+        <v>6343287</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,9 +3465,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3490,64 +3492,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130225961</v>
+        <v>130236453</v>
       </c>
       <c r="B29" t="n">
-        <v>92407</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576198</v>
+        <v>576441</v>
       </c>
       <c r="R29" t="n">
-        <v>6343287</v>
+        <v>6342906</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,19 +3584,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
         <v>130236380</v>
       </c>
       <c r="B30" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>130227842</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>130235558</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>130236402</v>
       </c>
       <c r="B5" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>130228760</v>
       </c>
       <c r="B6" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>130225954</v>
       </c>
       <c r="B7" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130226469</v>
       </c>
       <c r="B10" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130227694</v>
       </c>
       <c r="B15" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130227384</v>
       </c>
       <c r="B17" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130226405</v>
+        <v>130235360</v>
       </c>
       <c r="B18" t="n">
-        <v>79828</v>
+        <v>91759</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,37 +2337,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576198</v>
+        <v>576131</v>
       </c>
       <c r="R18" t="n">
-        <v>6343287</v>
+        <v>6343160</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2394,39 +2401,30 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2535,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130235360</v>
+        <v>130226405</v>
       </c>
       <c r="B20" t="n">
-        <v>91758</v>
+        <v>79828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,44 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576131</v>
+        <v>576198</v>
       </c>
       <c r="R20" t="n">
-        <v>6343160</v>
+        <v>6343287</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2610,40 +2601,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B21" t="n">
-        <v>91779</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,37 +2651,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R21" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2708,19 +2713,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,22 +2730,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>91780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,42 +2753,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R22" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,9 +2810,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,19 +2837,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130228309</v>
+        <v>130227753</v>
       </c>
       <c r="B23" t="n">
         <v>57849</v>
@@ -2878,21 +2878,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576518</v>
+        <v>576198</v>
       </c>
       <c r="R23" t="n">
-        <v>6342991</v>
+        <v>6343287</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2922,9 +2917,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2939,19 +2944,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130226031</v>
+        <v>130228309</v>
       </c>
       <c r="B24" t="n">
         <v>57849</v>
@@ -2987,14 +2992,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576189</v>
+        <v>576518</v>
       </c>
       <c r="R24" t="n">
-        <v>6343254</v>
+        <v>6342991</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3053,7 +3058,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227753</v>
+        <v>130226031</v>
       </c>
       <c r="B25" t="n">
         <v>57849</v>
@@ -3082,16 +3087,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576198</v>
+        <v>576189</v>
       </c>
       <c r="R25" t="n">
-        <v>6343287</v>
+        <v>6343254</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,19 +3148,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B26" t="n">
         <v>57849</v>
@@ -3188,10 +3188,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3200,13 +3209,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R26" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3244,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3245,7 +3254,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3272,7 +3281,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B27" t="n">
         <v>57849</v>
@@ -3300,19 +3309,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R27" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,7 +3396,7 @@
         <v>130225961</v>
       </c>
       <c r="B28" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>130236380</v>
       </c>
       <c r="B30" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>91782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R3" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,28 +872,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B4" t="n">
-        <v>91780</v>
+        <v>91761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,44 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R4" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +970,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -991,7 +991,7 @@
         <v>130236402</v>
       </c>
       <c r="B5" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>130228760</v>
       </c>
       <c r="B6" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,37 +1190,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130225954</v>
+        <v>130227038</v>
       </c>
       <c r="B7" t="n">
-        <v>92409</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576207</v>
+        <v>576189</v>
       </c>
       <c r="R7" t="n">
-        <v>6343282</v>
+        <v>6343133</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,7 +1295,7 @@
         <v>130226133</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,38 +1394,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130227038</v>
+        <v>130225954</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>92411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576189</v>
+        <v>576207</v>
       </c>
       <c r="R9" t="n">
-        <v>6343133</v>
+        <v>6343282</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130226469</v>
       </c>
       <c r="B10" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>130227799</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>130228206</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>130228644</v>
       </c>
       <c r="B13" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>130227745</v>
       </c>
       <c r="B14" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130227694</v>
       </c>
       <c r="B15" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>130226464</v>
       </c>
       <c r="B16" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>130227384</v>
       </c>
       <c r="B17" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130235360</v>
+        <v>130226405</v>
       </c>
       <c r="B18" t="n">
-        <v>91759</v>
+        <v>79830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,44 +2337,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576131</v>
+        <v>576198</v>
       </c>
       <c r="R18" t="n">
-        <v>6343160</v>
+        <v>6343287</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,40 +2394,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130226314</v>
+        <v>130235360</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>91761</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,42 +2444,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576147</v>
+        <v>576131</v>
       </c>
       <c r="R19" t="n">
-        <v>6343161</v>
+        <v>6343160</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2515,28 +2519,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226405</v>
+        <v>130226314</v>
       </c>
       <c r="B20" t="n">
-        <v>79828</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2549,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576198</v>
+        <v>576147</v>
       </c>
       <c r="R20" t="n">
-        <v>6343287</v>
+        <v>6343161</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,19 +2611,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,22 +2628,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>91782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,42 +2651,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R21" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2713,9 +2708,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,22 +2735,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B22" t="n">
-        <v>91780</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,37 +2758,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R22" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,19 +2820,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,22 +2837,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130227753</v>
+        <v>130228309</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,16 +2878,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576198</v>
+        <v>576518</v>
       </c>
       <c r="R23" t="n">
-        <v>6343287</v>
+        <v>6342991</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2917,19 +2922,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,22 +2939,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130228309</v>
+        <v>130226031</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2992,14 +2987,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576518</v>
+        <v>576189</v>
       </c>
       <c r="R24" t="n">
-        <v>6342991</v>
+        <v>6343254</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3058,10 +3053,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130226031</v>
+        <v>130227753</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,21 +3082,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576189</v>
+        <v>576198</v>
       </c>
       <c r="R25" t="n">
-        <v>6343254</v>
+        <v>6343287</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3131,9 +3121,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,22 +3148,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B26" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,19 +3188,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3209,13 +3200,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R26" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3244,7 +3235,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3254,7 +3245,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,10 +3300,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R27" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,7 +3396,7 @@
         <v>130225961</v>
       </c>
       <c r="B28" t="n">
-        <v>92409</v>
+        <v>92411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>130236453</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>130236380</v>
       </c>
       <c r="B30" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130227547</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130235558</v>
+        <v>130227842</v>
       </c>
       <c r="B3" t="n">
-        <v>91782</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,44 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576365</v>
+        <v>576457</v>
       </c>
       <c r="R3" t="n">
-        <v>6343031</v>
+        <v>6343001</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,29 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227842</v>
+        <v>130235558</v>
       </c>
       <c r="B4" t="n">
-        <v>91761</v>
+        <v>91782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,37 +894,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576457</v>
+        <v>576365</v>
       </c>
       <c r="R4" t="n">
-        <v>6343001</v>
+        <v>6343031</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,18 +969,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
         <v>130228760</v>
       </c>
       <c r="B6" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,38 +1190,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130227038</v>
+        <v>130225954</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>92415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,13 +1229,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576189</v>
+        <v>576207</v>
       </c>
       <c r="R7" t="n">
-        <v>6343133</v>
+        <v>6343282</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,37 +1393,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130225954</v>
+        <v>130227038</v>
       </c>
       <c r="B9" t="n">
-        <v>92411</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576207</v>
+        <v>576189</v>
       </c>
       <c r="R9" t="n">
-        <v>6343282</v>
+        <v>6343133</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,45 +1495,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130226469</v>
+        <v>130227799</v>
       </c>
       <c r="B10" t="n">
-        <v>92214</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576198</v>
+        <v>576368</v>
       </c>
       <c r="R10" t="n">
-        <v>6343287</v>
+        <v>6343022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,57 +1590,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Emelie Westerberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Emelie Westerberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130227799</v>
+        <v>130226469</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>92220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576368</v>
+        <v>576198</v>
       </c>
       <c r="R11" t="n">
-        <v>6343022</v>
+        <v>6343287</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,12 +1697,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emelie Westerberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emelie Westerberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130226405</v>
+        <v>130226314</v>
       </c>
       <c r="B18" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,37 +2337,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576198</v>
+        <v>576147</v>
       </c>
       <c r="R18" t="n">
-        <v>6343287</v>
+        <v>6343161</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2394,19 +2399,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,12 +2416,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2538,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226314</v>
+        <v>130226405</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576147</v>
+        <v>576198</v>
       </c>
       <c r="R20" t="n">
-        <v>6343161</v>
+        <v>6343287</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2611,9 +2601,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B26" t="n">
         <v>57851</v>
@@ -3188,10 +3188,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3200,13 +3209,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R26" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3244,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3245,7 +3254,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3272,7 +3281,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B27" t="n">
         <v>57851</v>
@@ -3300,19 +3309,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R27" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3393,52 +3393,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130225961</v>
+        <v>130236453</v>
       </c>
       <c r="B28" t="n">
-        <v>92411</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576198</v>
+        <v>576441</v>
       </c>
       <c r="R28" t="n">
-        <v>6343287</v>
+        <v>6342906</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,19 +3473,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3492,72 +3490,64 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130236453</v>
+        <v>130225961</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>92415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576441</v>
+        <v>576198</v>
       </c>
       <c r="R29" t="n">
-        <v>6342906</v>
+        <v>6343287</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,9 +3574,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -1495,45 +1495,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130227799</v>
+        <v>130226469</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>92220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576368</v>
+        <v>576198</v>
       </c>
       <c r="R10" t="n">
-        <v>6343022</v>
+        <v>6343287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,57 +1590,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emelie Westerberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emelie Westerberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130226469</v>
+        <v>130227799</v>
       </c>
       <c r="B11" t="n">
-        <v>92220</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576198</v>
+        <v>576368</v>
       </c>
       <c r="R11" t="n">
-        <v>6343287</v>
+        <v>6343022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,22 +1697,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Emelie Westerberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Emelie Westerberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228206</v>
+        <v>130228644</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,42 +1720,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576360</v>
+        <v>576518</v>
       </c>
       <c r="R12" t="n">
-        <v>6342961</v>
+        <v>6342991</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,19 +1777,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,19 +1794,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228644</v>
+        <v>130227745</v>
       </c>
       <c r="B13" t="n">
         <v>79830</v>
@@ -1852,17 +1837,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gräsgölen, Gräsgölen, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576518</v>
+        <v>576451</v>
       </c>
       <c r="R13" t="n">
-        <v>6342991</v>
+        <v>6343018</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1918,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130227745</v>
+        <v>130228206</v>
       </c>
       <c r="B14" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,37 +1914,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Gräsgölen, Gräsgölen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576451</v>
+        <v>576360</v>
       </c>
       <c r="R14" t="n">
-        <v>6343018</v>
+        <v>6342961</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,9 +1976,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,12 +2003,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130226314</v>
+        <v>130235360</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,42 +2337,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
+          <t>Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576147</v>
+        <v>576131</v>
       </c>
       <c r="R18" t="n">
-        <v>6343161</v>
+        <v>6343160</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2410,28 +2412,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130235360</v>
+        <v>130226405</v>
       </c>
       <c r="B19" t="n">
-        <v>91761</v>
+        <v>79830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,44 +2442,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mönsterås kommun, Sm</t>
+          <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576131</v>
+        <v>576198</v>
       </c>
       <c r="R19" t="n">
-        <v>6343160</v>
+        <v>6343287</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,40 +2499,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226405</v>
+        <v>130226314</v>
       </c>
       <c r="B20" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2549,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576198</v>
+        <v>576147</v>
       </c>
       <c r="R20" t="n">
-        <v>6343287</v>
+        <v>6343161</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,19 +2611,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,22 +2628,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B21" t="n">
-        <v>91782</v>
+        <v>57851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,37 +2651,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R21" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2708,19 +2713,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,22 +2730,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>91782</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,42 +2753,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R22" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,9 +2810,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,12 +2837,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130226031</v>
+        <v>130227753</v>
       </c>
       <c r="B24" t="n">
         <v>57851</v>
@@ -2980,21 +2980,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576189</v>
+        <v>576198</v>
       </c>
       <c r="R24" t="n">
-        <v>6343254</v>
+        <v>6343287</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3024,9 +3019,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,19 +3046,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130227753</v>
+        <v>130226031</v>
       </c>
       <c r="B25" t="n">
         <v>57851</v>
@@ -3082,16 +3087,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576198</v>
+        <v>576189</v>
       </c>
       <c r="R25" t="n">
-        <v>6343287</v>
+        <v>6343254</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3121,19 +3131,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3148,19 +3148,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B26" t="n">
         <v>57851</v>
@@ -3188,19 +3188,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3209,13 +3200,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R26" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3244,7 +3235,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3254,7 +3245,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,7 +3272,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B27" t="n">
         <v>57851</v>
@@ -3309,10 +3300,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R27" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 59243-2025 artfynd.xlsx
+++ b/artfynd/A 59243-2025 artfynd.xlsx
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130227640</v>
+        <v>130226508</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>91782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,42 +2651,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576418</v>
+        <v>576198</v>
       </c>
       <c r="R21" t="n">
-        <v>6343043</v>
+        <v>6343287</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2713,9 +2708,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,22 +2735,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130226508</v>
+        <v>130227640</v>
       </c>
       <c r="B22" t="n">
-        <v>91782</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,37 +2758,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilla Lomsgölen, Lilla Lomsgölen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576198</v>
+        <v>576418</v>
       </c>
       <c r="R22" t="n">
-        <v>6343287</v>
+        <v>6343043</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,19 +2820,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,12 +2837,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130226739</v>
+        <v>130226330</v>
       </c>
       <c r="B26" t="n">
         <v>57851</v>
@@ -3188,10 +3188,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3200,13 +3209,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576238</v>
+        <v>576175</v>
       </c>
       <c r="R26" t="n">
-        <v>6343215</v>
+        <v>6343207</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3244,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3245,7 +3254,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3272,7 +3281,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130226330</v>
+        <v>130226739</v>
       </c>
       <c r="B27" t="n">
         <v>57851</v>
@@ -3300,19 +3309,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576175</v>
+        <v>576238</v>
       </c>
       <c r="R27" t="n">
-        <v>6343207</v>
+        <v>6343215</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
